--- a/product_selector_out/STM32H5E4-5F4.xlsx
+++ b/product_selector_out/STM32H5E4-5F4.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5675,9 +5675,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -5715,7 +5715,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5725,12 +5725,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5750,7 +5750,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="T12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5765,22 +5765,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5815,12 +5815,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH12" s="8" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5865,7 +5865,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ12" s="8" t="inlineStr">
+      <c r="AQ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5890,19 +5890,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AV12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -5925,52 +5925,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL12" s="8" t="inlineStr">
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5985,9 +5985,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6012,9 +6012,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -6052,7 +6052,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6062,12 +6062,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6087,7 +6087,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="T13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6102,22 +6102,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6152,12 +6152,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH13" s="8" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6202,7 +6202,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ13" s="8" t="inlineStr">
+      <c r="AQ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6227,19 +6227,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AV13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -6262,52 +6262,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL13" s="8" t="inlineStr">
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6322,9 +6322,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6349,9 +6349,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -6389,7 +6389,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6399,12 +6399,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6424,7 +6424,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="T14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6439,22 +6439,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6489,12 +6489,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH14" s="8" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6539,7 +6539,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ14" s="8" t="inlineStr">
+      <c r="AQ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6564,19 +6564,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AV14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -6599,52 +6599,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL14" s="8" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6659,9 +6659,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -6726,7 +6726,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6736,12 +6736,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6761,7 +6761,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="T15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6776,22 +6776,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6826,12 +6826,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH15" s="8" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6876,7 +6876,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ15" s="8" t="inlineStr">
+      <c r="AQ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6911,9 +6911,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -6936,52 +6936,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL15" s="8" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7023,9 +7023,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7063,7 +7063,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7073,12 +7073,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7098,7 +7098,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="T16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7113,22 +7113,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7163,12 +7163,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH16" s="8" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7213,7 +7213,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ16" s="8" t="inlineStr">
+      <c r="AQ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7243,14 +7243,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -7273,52 +7273,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL16" s="8" t="inlineStr">
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7333,9 +7333,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7360,9 +7360,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -7400,7 +7400,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7410,12 +7410,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7435,7 +7435,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="T17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7450,22 +7450,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7500,12 +7500,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH17" s="8" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7550,7 +7550,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ17" s="8" t="inlineStr">
+      <c r="AQ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7580,14 +7580,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -7610,52 +7610,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL17" s="8" t="inlineStr">
+      <c r="BC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7670,9 +7670,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7697,9 +7697,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -7737,7 +7737,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7747,12 +7747,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7772,7 +7772,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="T18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7787,22 +7787,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7837,12 +7837,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH18" s="8" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7887,7 +7887,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ18" s="8" t="inlineStr">
+      <c r="AQ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7912,19 +7912,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AV18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -7947,52 +7947,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL18" s="8" t="inlineStr">
+      <c r="BC18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8007,9 +8007,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8034,9 +8034,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -8074,7 +8074,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8084,12 +8084,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8109,7 +8109,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="T19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8124,22 +8124,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8174,12 +8174,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH19" s="8" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8224,7 +8224,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ19" s="8" t="inlineStr">
+      <c r="AQ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8254,14 +8254,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -8284,52 +8284,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL19" s="8" t="inlineStr">
+      <c r="BC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8344,9 +8344,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8371,9 +8371,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -8411,7 +8411,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8421,12 +8421,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8446,7 +8446,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="T20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8461,22 +8461,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8511,12 +8511,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH20" s="8" t="inlineStr">
+      <c r="AG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8561,7 +8561,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ20" s="8" t="inlineStr">
+      <c r="AQ20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8591,14 +8591,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -8621,52 +8621,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL20" s="8" t="inlineStr">
+      <c r="BC20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8681,9 +8681,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -8748,7 +8748,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8758,12 +8758,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8783,7 +8783,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="T21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8798,22 +8798,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8848,12 +8848,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH21" s="8" t="inlineStr">
+      <c r="AG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8898,7 +8898,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ21" s="8" t="inlineStr">
+      <c r="AQ21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8933,9 +8933,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -8958,52 +8958,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL21" s="8" t="inlineStr">
+      <c r="BC21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9045,7 +9045,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9085,7 +9085,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9095,12 +9095,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9120,7 +9120,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="T22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9135,22 +9135,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9185,12 +9185,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH22" s="8" t="inlineStr">
+      <c r="AG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9235,7 +9235,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ22" s="8" t="inlineStr">
+      <c r="AQ22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9270,9 +9270,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -9295,52 +9295,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL22" s="8" t="inlineStr">
+      <c r="BC22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9382,9 +9382,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -9422,7 +9422,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9432,12 +9432,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9457,7 +9457,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="T23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9472,22 +9472,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9522,12 +9522,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH23" s="8" t="inlineStr">
+      <c r="AG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9572,7 +9572,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ23" s="8" t="inlineStr">
+      <c r="AQ23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9602,14 +9602,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -9632,52 +9632,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL23" s="8" t="inlineStr">
+      <c r="BC23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9692,9 +9692,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9747,7 +9747,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32H5E4AK</t>
+          <t>STM32H5E4VJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9762,19 +9762,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32H5E4IK</t>
+          <t>STM32H5E4VJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9784,14 +9784,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32H5E4VK</t>
+          <t>STM32H5E4AJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9806,19 +9806,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32H5E4VJ</t>
+          <t>STM32H5E4AJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9828,14 +9828,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32H5E4ZJ</t>
+          <t>STM32H5F4AJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9850,19 +9850,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32H5F4IJ</t>
+          <t>STM32H5F4AJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9872,139 +9872,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32H5E4ZK</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32H5F4VJ</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32H5F4ZJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32H5E4AJ</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32H5F4AJ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32H5E4IJ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H5E4-5F4.xlsx
+++ b/product_selector_out/STM32H5E4-5F4.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -5675,9 +5675,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -5715,7 +5715,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5725,12 +5725,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5750,7 +5750,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T12" s="7" t="inlineStr">
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5765,22 +5765,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5815,12 +5815,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH12" s="7" t="inlineStr">
+      <c r="AG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5865,7 +5865,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ12" s="7" t="inlineStr">
+      <c r="AQ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5890,19 +5890,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AV12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -5925,52 +5925,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL12" s="7" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5985,9 +5985,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6012,9 +6012,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -6052,7 +6052,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6062,12 +6062,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6087,7 +6087,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T13" s="7" t="inlineStr">
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6102,22 +6102,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6152,12 +6152,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH13" s="7" t="inlineStr">
+      <c r="AG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6202,7 +6202,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ13" s="7" t="inlineStr">
+      <c r="AQ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6227,19 +6227,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AV13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -6262,52 +6262,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL13" s="7" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6322,9 +6322,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6349,9 +6349,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -6389,7 +6389,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6399,12 +6399,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6424,7 +6424,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T14" s="7" t="inlineStr">
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6439,22 +6439,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6489,12 +6489,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH14" s="7" t="inlineStr">
+      <c r="AG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6539,7 +6539,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ14" s="7" t="inlineStr">
+      <c r="AQ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6564,19 +6564,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AV14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -6599,52 +6599,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL14" s="7" t="inlineStr">
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6659,9 +6659,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -6726,7 +6726,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6736,12 +6736,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6761,7 +6761,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T15" s="7" t="inlineStr">
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6776,22 +6776,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6826,12 +6826,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH15" s="7" t="inlineStr">
+      <c r="AG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6876,7 +6876,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ15" s="7" t="inlineStr">
+      <c r="AQ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6936,52 +6936,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL15" s="7" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7023,9 +7023,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7063,7 +7063,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7073,12 +7073,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7098,7 +7098,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T16" s="7" t="inlineStr">
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7113,22 +7113,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7163,12 +7163,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH16" s="7" t="inlineStr">
+      <c r="AG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7213,7 +7213,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ16" s="7" t="inlineStr">
+      <c r="AQ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7243,14 +7243,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -7273,52 +7273,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL16" s="7" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7333,9 +7333,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7360,9 +7360,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -7400,7 +7400,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7410,12 +7410,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7435,7 +7435,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T17" s="7" t="inlineStr">
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7450,22 +7450,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7500,12 +7500,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH17" s="7" t="inlineStr">
+      <c r="AG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7550,7 +7550,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ17" s="7" t="inlineStr">
+      <c r="AQ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7580,14 +7580,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -7610,52 +7610,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL17" s="7" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7670,9 +7670,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7697,9 +7697,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -7737,7 +7737,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7747,12 +7747,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7772,7 +7772,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T18" s="7" t="inlineStr">
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7787,22 +7787,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7837,12 +7837,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH18" s="7" t="inlineStr">
+      <c r="AG18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7887,7 +7887,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ18" s="7" t="inlineStr">
+      <c r="AQ18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7912,19 +7912,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AV18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -7947,52 +7947,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL18" s="7" t="inlineStr">
+      <c r="BC18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8007,9 +8007,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8034,9 +8034,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -8074,7 +8074,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8084,12 +8084,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8109,7 +8109,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T19" s="7" t="inlineStr">
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8124,22 +8124,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8174,12 +8174,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH19" s="7" t="inlineStr">
+      <c r="AG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8224,7 +8224,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ19" s="7" t="inlineStr">
+      <c r="AQ19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8254,14 +8254,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -8284,52 +8284,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL19" s="7" t="inlineStr">
+      <c r="BC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8344,9 +8344,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8371,9 +8371,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -8411,7 +8411,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8421,12 +8421,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8446,7 +8446,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T20" s="7" t="inlineStr">
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8461,22 +8461,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8511,12 +8511,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH20" s="7" t="inlineStr">
+      <c r="AG20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8561,7 +8561,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ20" s="7" t="inlineStr">
+      <c r="AQ20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8591,14 +8591,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -8621,52 +8621,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL20" s="7" t="inlineStr">
+      <c r="BC20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8681,9 +8681,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -8748,7 +8748,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8758,12 +8758,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8783,7 +8783,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T21" s="7" t="inlineStr">
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8798,22 +8798,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8848,12 +8848,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH21" s="7" t="inlineStr">
+      <c r="AG21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8898,7 +8898,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ21" s="7" t="inlineStr">
+      <c r="AQ21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8958,52 +8958,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL21" s="7" t="inlineStr">
+      <c r="BC21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9045,7 +9045,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9085,7 +9085,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9095,12 +9095,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9120,7 +9120,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T22" s="7" t="inlineStr">
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9135,22 +9135,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="7" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9185,12 +9185,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH22" s="7" t="inlineStr">
+      <c r="AG22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9235,7 +9235,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ22" s="7" t="inlineStr">
+      <c r="AQ22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9295,52 +9295,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL22" s="7" t="inlineStr">
+      <c r="BC22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9382,9 +9382,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -9422,7 +9422,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9432,12 +9432,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9457,7 +9457,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="T23" s="7" t="inlineStr">
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9472,22 +9472,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9522,12 +9522,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH23" s="7" t="inlineStr">
+      <c r="AG23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9572,7 +9572,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ23" s="7" t="inlineStr">
+      <c r="AQ23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9602,14 +9602,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -9632,52 +9632,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL23" s="7" t="inlineStr">
+      <c r="BC23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9692,9 +9692,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9747,7 +9747,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32H5E4VJ</t>
+          <t>STM32H5E4AK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9769,7 +9769,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32H5E4VJ</t>
+          <t>STM32H5E4AK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9791,7 +9791,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32H5E4AJ</t>
+          <t>STM32H5E4IK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9813,7 +9813,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32H5E4AJ</t>
+          <t>STM32H5E4IK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9835,7 +9835,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32H5F4AJ</t>
+          <t>STM32H5E4VK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9850,29 +9850,425 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>STM32H5E4VK</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32H5E4VJ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32H5E4VJ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32H5E4ZJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32H5E4ZJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32H5F4IJ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32H5F4IJ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32H5E4ZK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32H5E4ZK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32H5F4VJ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32H5F4VJ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32H5F4ZJ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32H5F4ZJ</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32H5E4AJ</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32H5E4AJ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>STM32H5F4AJ</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32H5F4AJ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Supply Voltage (V) max</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32H5E4IJ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32H5E4IJ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H5E4-5F4.xlsx
+++ b/product_selector_out/STM32H5E4-5F4.xlsx
@@ -1338,7 +1338,7 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H5E4-5F4.xlsx
+++ b/product_selector_out/STM32H5E4-5F4.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO23"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.59765625" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -2686,6 +2713,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -3023,6 +3055,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -3360,6 +3397,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -3697,6 +3739,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -4034,6 +4081,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -4371,6 +4423,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -4708,6 +4765,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -5045,12 +5107,17 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -5073,12 +5140,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -5093,9 +5162,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -5143,7 +5211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO23"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5213,6 +5281,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5556,6 +5625,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -5653,6 +5727,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5985,7 +6060,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6322,7 +6402,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6659,7 +6744,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6996,7 +7086,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7333,7 +7428,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7670,7 +7770,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8007,7 +8112,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8344,7 +8454,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8681,7 +8796,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9018,7 +9138,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9355,7 +9480,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9692,7 +9822,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9700,8 +9835,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
